--- a/EN_macroed-merged.xlsx
+++ b/EN_macroed-merged.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ62"/>
+  <dimension ref="A1:CG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,7 +427,7 @@
           <t>Con l'attività che hai descritto: {attivita}  su quali obiettivi di apprendimento relativi a informatica/ pensiero computazionale/ coding si lavora?</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Con l'attività che hai descritto, su quali altri obiettivi di apprendimento (espressi in termini di conoscenza, abilità, competenze) si lavora?</t>
         </is>
@@ -466,217 +466,260 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- robot</t>
+          <t>materiali/strumenti fisici
+robot</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- corpo</t>
+          <t>materiali/strumenti fisici
+corpo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- pc/tablet</t>
+          <t>materiali/strumenti fisici
+pc/tablet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- lim</t>
+          <t>materiali/strumenti fisici
+lim</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali di ambiente/movimento in cui si opera per le attività</t>
+          <t>materiali/strumenti fisici
+materiali di ambiente/movimento in cui si opera per le attività</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- carte/blocchi</t>
+          <t>materiali/strumenti fisici
+carte/blocchi</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>attività -- altro</t>
+          <t>attività
+altro</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>attività -- contenuti algoritmici</t>
+          <t>attività
+contenuti algoritmici</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>attività -- movimento e percorsi</t>
+          <t>attività
+movimento e percorsi</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>attività -- videogiochi</t>
+          <t>attività
+videogiochi</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>attività -- uso tecnologia e sviluppo contenuti</t>
+          <t>attività
+uso tecnologia e sviluppo contenuti</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>attività -- storytelling</t>
+          <t>attività
+storytelling</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>attività -- unplugged</t>
+          <t>attività
+unplugged</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>attività -- processi di informatica</t>
+          <t>attività
+processi di informatica</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>attività -- verifica e correzione</t>
+          <t>attività
+verifica e correzione</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>attività -- pixel art</t>
+          <t>attività
+pixel art</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>attività -- programmazione</t>
+          <t>attività
+programmazione</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>attività -- coding</t>
+          <t>attività
+coding</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- intelligenza artificiale</t>
+          <t>obiettivi disciplinari
+intelligenza artificiale</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- geografia</t>
+          <t>interdisciplinarità
+geografia</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- software di creazione/ricerca contenuti</t>
+          <t>piattaforma/ ambiente
+software di creazione/ricerca contenuti</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- ambiente pixel art</t>
+          <t>piattaforma/ ambiente
+ambiente pixel art</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- scratch</t>
+          <t>piattaforma/ ambiente
+scratch</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- geometria dinamica</t>
+          <t>piattaforma/ ambiente
+geometria dinamica</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- code.org / programma il futuro</t>
+          <t>piattaforma/ ambiente
+code.org / programma il futuro</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- google workspace</t>
+          <t>piattaforma/ ambiente
+google workspace</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- carte/blocchi programmazione</t>
+          <t>piattaforma/ ambiente
+carte/blocchi programmazione</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>metodologia -- sì</t>
+          <t>metodologia
+sì</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>metodologia -- forse</t>
+          <t>metodologia
+forse</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -691,187 +734,204 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (generica)</t>
+          <t>obiettivi disciplinari
+programmazione (generica)</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- logica</t>
+          <t>obiettivi pertinenti
+logica</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- verifica/ correzione</t>
+          <t>obiettivi disciplinari
+verifica/ correzione</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- pratiche</t>
+          <t>obiettivi disciplinari
+pratiche</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- metodi</t>
+          <t>obiettivi disciplinari
+metodi</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- progettazione</t>
+          <t>obiettivi pertinenti
+progettazione</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>risposta generica d2 -- vuoto-d2</t>
+          <t>risposta generica d2
+vuoto-d2</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>risposta generica d2 -- generico-d2</t>
+          <t>risposta generica d2
+generico-d2</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>focus d2 -- studente</t>
+          <t>focus d2
+studente</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>focus d2 -- insegnante</t>
+          <t>focus d2
+insegnante</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>focus d2 -- contenuto</t>
+          <t>focus d2
+contenuto</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività digitale</t>
+          <t>obiettivi pertinenti
+creatività digitale</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- interdisciplinarità</t>
+          <t>interdisciplinarità
+interdisciplinarità</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>D3_ID</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>D3_Domanda 3</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>D3_ID</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>D3_Domanda 3</t>
+          <t>interdisciplinarità
+educazione fisica</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- comunicazione</t>
+          <t>interdisciplinarità
+scienze</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+tecnologia</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- educazione fisica</t>
+          <t>interdisciplinarità
+lingua straniera</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- scienze</t>
+          <t>interdisciplinarità
+educazione civica</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- tecnologia</t>
+          <t>interdisciplinarità
+storia</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- lingua straniera</t>
+          <t>obiettivi disciplinari
+rappresentazione dell'informazione</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- educazione civica</t>
+          <t>risposta generica d3
+vuoto-d3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- storia</t>
+          <t>risposta generica d3
+generico-d3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- rappresentazione dell’informazione</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>risposta generica d3 -- vuoto-d3</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>risposta generica d3 -- generico-d3</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>risposta generica d3 -- copia risposta 2</t>
+          <t>risposta generica d3
+copia risposta 2</t>
         </is>
       </c>
     </row>
@@ -932,13 +992,13 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -974,7 +1034,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>X</t>
@@ -1014,12 +1078,10 @@
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="n">
+      <c r="BU3" t="n">
         <v>631</v>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>Sapersi esprimere e comunicare utilizzando codici e linguaggi diversi
 Analizzare e rappresentare processi utilizzando modelli logici
@@ -1027,11 +1089,9 @@
 Utilizzare trasversalmente le conoscenze</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
@@ -1040,9 +1100,6 @@
       <c r="CE3" t="inlineStr"/>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
-      <c r="CJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1144,27 +1201,24 @@
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="n">
+      <c r="BU4" t="n">
         <v>636</v>
       </c>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="inlineStr"/>
       <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr"/>
-      <c r="CJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1281,18 +1335,18 @@
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="n">
+      <c r="BU5" t="n">
         <v>638</v>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>Matematica
 Geometria
 Geografia</t>
         </is>
       </c>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
@@ -1302,9 +1356,6 @@
       <c r="CE5" t="inlineStr"/>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1353,7 +1404,11 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1378,11 +1433,7 @@
         </is>
       </c>
       <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1410,16 +1461,16 @@
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="n">
+      <c r="BU6" t="n">
         <v>643</v>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>Capacità di produrre ipotesi; cercare soluzioni (ordinate in azioni in successione) in situazioni di proble solving</t>
         </is>
       </c>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
@@ -1429,9 +1480,6 @@
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1541,27 +1589,24 @@
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
       <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="n">
+      <c r="BU7" t="n">
         <v>646</v>
       </c>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr"/>
       <c r="CA7" t="inlineStr"/>
       <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1616,7 +1661,11 @@
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1641,14 +1690,14 @@
         </is>
       </c>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr">
@@ -1677,16 +1726,16 @@
       </c>
       <c r="BS8" t="inlineStr"/>
       <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="n">
+      <c r="BU8" t="n">
         <v>652</v>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>Saper utilizzare programmi informatici per sviluppare la logica, pensiero critico</t>
         </is>
       </c>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="inlineStr"/>
       <c r="CA8" t="inlineStr"/>
@@ -1696,9 +1745,6 @@
       <c r="CE8" t="inlineStr"/>
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1775,7 +1821,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -1821,11 +1871,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1873,12 +1919,10 @@
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="n">
+      <c r="BU9" t="n">
         <v>654</v>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>-Inventare oggetti Smart ( video);
 -Sperimentare in prima persona;
@@ -1893,22 +1937,21 @@
 -Imparare a scrivere i comandi in ordine e risolvere i problemi usando algoritmi.</t>
         </is>
       </c>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="inlineStr"/>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CE9" t="inlineStr"/>
       <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr"/>
-      <c r="CJ9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1982,7 +2025,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -2037,36 +2084,29 @@
       <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="n">
+      <c r="BU10" t="n">
         <v>658</v>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>Uso dell'Inglese per gli anni passati  e del saper utilizzare le risorse dei filmati anche in termini di esercitazione alla lettura all'impronta, alla descrizione e  comprensione globale di ciò che avviene e si voglia sottolineare, saper modificare la velocità di trasmissione e  la lingua,  catturare immagini con lo strumento cattura e annota del computer  e saper restituire sul quaderno le attività grafiche dello stage, dell'area di lavoro e  dei blocchi di alcuni esercizi tipo come promemoria e quaderno di bordo delle attività.</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
       <c r="BZ10" t="inlineStr"/>
-      <c r="CA10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CB10" t="inlineStr"/>
       <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="inlineStr"/>
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
-      <c r="CI10" t="inlineStr"/>
-      <c r="CJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2206,33 +2246,30 @@
       </c>
       <c r="BS11" t="inlineStr"/>
       <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="n">
+      <c r="BU11" t="n">
         <v>659</v>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>Modella il modo in cui i programmi memorizzano e manipolano i dati utilizzando numeri o altri simboli per rappresentare le informazioni. 
 - Scomporre  i passaggi necessari per risolvere un problema in una sequenza precisa di istruzioni.</t>
         </is>
       </c>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
       <c r="BY11" t="inlineStr"/>
       <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CE11" t="inlineStr"/>
       <c r="CF11" t="inlineStr"/>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr"/>
-      <c r="CI11" t="inlineStr"/>
-      <c r="CJ11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2296,7 +2333,11 @@
         </is>
       </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -2338,11 +2379,7 @@
         </is>
       </c>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
@@ -2378,32 +2415,29 @@
       <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="inlineStr"/>
       <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="n">
+      <c r="BU12" t="n">
         <v>662</v>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>obiettivo dell'educazione alla sicurezza ( educazione civica Digital)</t>
         </is>
       </c>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CE12" t="inlineStr"/>
       <c r="CF12" t="inlineStr"/>
       <c r="CG12" t="inlineStr"/>
-      <c r="CH12" t="inlineStr"/>
-      <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2449,7 +2483,11 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
@@ -2482,11 +2520,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
         <is>
@@ -2518,17 +2552,17 @@
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr"/>
       <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
-      <c r="BW13" t="n">
+      <c r="BU13" t="n">
         <v>668</v>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>Comprendere i principi della programmazione, identificare i problemi, risolverli.
 Saper utilizzare il linguaggio di programmazione per costruire oggetti, realizzare disegni e far muovere robot.</t>
         </is>
       </c>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
@@ -2538,9 +2572,6 @@
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="inlineStr"/>
       <c r="CG13" t="inlineStr"/>
-      <c r="CH13" t="inlineStr"/>
-      <c r="CI13" t="inlineStr"/>
-      <c r="CJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2667,12 +2698,10 @@
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="inlineStr"/>
       <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="n">
+      <c r="BU14" t="n">
         <v>680</v>
       </c>
-      <c r="BX14" t="inlineStr">
+      <c r="BV14" t="inlineStr">
         <is>
           <t>Leggere e comprendere istruzioni
 Imparare ad imparare
@@ -2680,6 +2709,8 @@
 Pensiero creativo</t>
         </is>
       </c>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="inlineStr"/>
@@ -2689,9 +2720,6 @@
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="inlineStr"/>
       <c r="CG14" t="inlineStr"/>
-      <c r="CH14" t="inlineStr"/>
-      <c r="CI14" t="inlineStr"/>
-      <c r="CJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2741,7 +2769,11 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
@@ -2802,28 +2834,24 @@
       <c r="BN15" t="inlineStr"/>
       <c r="BO15" t="inlineStr"/>
       <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="n">
+        <v>681</v>
+      </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BW15" t="n">
-        <v>681</v>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
           <t>Capacità ci cooperare, rielaborazione dei propri saperi.</t>
         </is>
       </c>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="inlineStr"/>
       <c r="CA15" t="inlineStr"/>
@@ -2833,9 +2861,6 @@
       <c r="CE15" t="inlineStr"/>
       <c r="CF15" t="inlineStr"/>
       <c r="CG15" t="inlineStr"/>
-      <c r="CH15" t="inlineStr"/>
-      <c r="CI15" t="inlineStr"/>
-      <c r="CJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2993,27 +3018,24 @@
       <c r="BR16" t="inlineStr"/>
       <c r="BS16" t="inlineStr"/>
       <c r="BT16" t="inlineStr"/>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
-      <c r="BW16" t="n">
+      <c r="BU16" t="n">
         <v>682</v>
       </c>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="inlineStr"/>
       <c r="CB16" t="inlineStr"/>
       <c r="CC16" t="inlineStr"/>
       <c r="CD16" t="inlineStr"/>
-      <c r="CE16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF16" t="inlineStr"/>
       <c r="CG16" t="inlineStr"/>
-      <c r="CH16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI16" t="inlineStr"/>
-      <c r="CJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3085,7 +3107,11 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
@@ -3124,11 +3150,7 @@
         </is>
       </c>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr">
         <is>
@@ -3152,16 +3174,16 @@
       <c r="BR17" t="inlineStr"/>
       <c r="BS17" t="inlineStr"/>
       <c r="BT17" t="inlineStr"/>
-      <c r="BU17" t="inlineStr"/>
-      <c r="BV17" t="inlineStr"/>
-      <c r="BW17" t="n">
+      <c r="BU17" t="n">
         <v>688</v>
       </c>
-      <c r="BX17" t="inlineStr">
+      <c r="BV17" t="inlineStr">
         <is>
           <t>Si lavora sulla conoscenza del significato di contorno di una superficie piana, lato, ma anche sviluppando abilità di programmazione e competenze per quanto riguarda spazio e figure.</t>
         </is>
       </c>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="inlineStr"/>
       <c r="CA17" t="inlineStr"/>
@@ -3171,9 +3193,6 @@
       <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="inlineStr"/>
       <c r="CG17" t="inlineStr"/>
-      <c r="CH17" t="inlineStr"/>
-      <c r="CI17" t="inlineStr"/>
-      <c r="CJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3310,17 +3329,17 @@
         </is>
       </c>
       <c r="BT18" t="inlineStr"/>
-      <c r="BU18" t="inlineStr"/>
-      <c r="BV18" t="inlineStr"/>
-      <c r="BW18" t="n">
+      <c r="BU18" t="n">
         <v>690</v>
       </c>
-      <c r="BX18" t="inlineStr">
+      <c r="BV18" t="inlineStr">
         <is>
           <t>Usa siti specifici dedicati a scuola e studenti di età simile.
 Inizia a riconoscere e scegliere tra notizie-foto vere o false</t>
         </is>
       </c>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="inlineStr"/>
       <c r="CA18" t="inlineStr"/>
@@ -3330,9 +3349,6 @@
       <c r="CE18" t="inlineStr"/>
       <c r="CF18" t="inlineStr"/>
       <c r="CG18" t="inlineStr"/>
-      <c r="CH18" t="inlineStr"/>
-      <c r="CI18" t="inlineStr"/>
-      <c r="CJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3383,7 +3399,11 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
@@ -3453,23 +3473,19 @@
       <c r="BQ19" t="inlineStr"/>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="inlineStr"/>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr"/>
-      <c r="BV19" t="inlineStr"/>
-      <c r="BW19" t="n">
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="n">
         <v>698</v>
       </c>
-      <c r="BX19" t="inlineStr">
+      <c r="BV19" t="inlineStr">
         <is>
           <t>Conoscere lo spazio e i riferimenti spaziali.
 Sapersi orientare.
 Collaborare con gli altri.</t>
         </is>
       </c>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="inlineStr"/>
       <c r="CA19" t="inlineStr"/>
@@ -3479,9 +3495,6 @@
       <c r="CE19" t="inlineStr"/>
       <c r="CF19" t="inlineStr"/>
       <c r="CG19" t="inlineStr"/>
-      <c r="CH19" t="inlineStr"/>
-      <c r="CI19" t="inlineStr"/>
-      <c r="CJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3611,12 +3624,10 @@
       <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="inlineStr"/>
       <c r="BT20" t="inlineStr"/>
-      <c r="BU20" t="inlineStr"/>
-      <c r="BV20" t="inlineStr"/>
-      <c r="BW20" t="n">
+      <c r="BU20" t="n">
         <v>706</v>
       </c>
-      <c r="BX20" t="inlineStr">
+      <c r="BV20" t="inlineStr">
         <is>
           <t>Mettere in relazione il pensare con il fare.
 Rappresentare dati dell'osservazione attraverso diagrammi , testi, tabelle, disegni.
@@ -3624,6 +3635,8 @@
 Descrivere lo svolgersi dei fatti e formulare domande, anche sulla base di ipotesi personali.</t>
         </is>
       </c>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="inlineStr"/>
       <c r="CA20" t="inlineStr"/>
@@ -3633,9 +3646,6 @@
       <c r="CE20" t="inlineStr"/>
       <c r="CF20" t="inlineStr"/>
       <c r="CG20" t="inlineStr"/>
-      <c r="CH20" t="inlineStr"/>
-      <c r="CI20" t="inlineStr"/>
-      <c r="CJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3746,17 +3756,15 @@
       </c>
       <c r="BR21" t="inlineStr"/>
       <c r="BS21" t="inlineStr"/>
-      <c r="BT21" t="inlineStr"/>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr"/>
-      <c r="BW21" t="n">
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BU21" t="n">
         <v>717</v>
       </c>
-      <c r="BX21" t="inlineStr">
+      <c r="BV21" t="inlineStr">
         <is>
           <t>Competenza alfabetico funzionale
 Competenza matematica e competenza in scienze ,tecnologie e ingegneria
@@ -3764,30 +3772,29 @@
 Competenza personale,sociale e capacità di imparare ad imparare.</t>
         </is>
       </c>
-      <c r="BY21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BZ21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr"/>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
       <c r="CD21" t="inlineStr"/>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="inlineStr"/>
       <c r="CG21" t="inlineStr"/>
-      <c r="CH21" t="inlineStr"/>
-      <c r="CI21" t="inlineStr"/>
-      <c r="CJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3908,16 +3915,16 @@
       <c r="BR22" t="inlineStr"/>
       <c r="BS22" t="inlineStr"/>
       <c r="BT22" t="inlineStr"/>
-      <c r="BU22" t="inlineStr"/>
-      <c r="BV22" t="inlineStr"/>
-      <c r="BW22" t="n">
+      <c r="BU22" t="n">
         <v>722</v>
       </c>
-      <c r="BX22" t="inlineStr">
+      <c r="BV22" t="inlineStr">
         <is>
           <t>conoscenza, abilità e competenze</t>
         </is>
       </c>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="inlineStr"/>
       <c r="CA22" t="inlineStr"/>
@@ -3925,15 +3932,12 @@
       <c r="CC22" t="inlineStr"/>
       <c r="CD22" t="inlineStr"/>
       <c r="CE22" t="inlineStr"/>
-      <c r="CF22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CG22" t="inlineStr"/>
-      <c r="CH22" t="inlineStr"/>
-      <c r="CI22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4065,12 +4069,10 @@
       <c r="BR23" t="inlineStr"/>
       <c r="BS23" t="inlineStr"/>
       <c r="BT23" t="inlineStr"/>
-      <c r="BU23" t="inlineStr"/>
-      <c r="BV23" t="inlineStr"/>
-      <c r="BW23" t="n">
+      <c r="BU23" t="n">
         <v>723</v>
       </c>
-      <c r="BX23" t="inlineStr">
+      <c r="BV23" t="inlineStr">
         <is>
           <t>Italiano
 Ascolto e parlato
@@ -4093,30 +4095,29 @@
 Descrivere semplici fenome</t>
         </is>
       </c>
-      <c r="BY23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BZ23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr"/>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
       <c r="CD23" t="inlineStr"/>
       <c r="CE23" t="inlineStr"/>
       <c r="CF23" t="inlineStr"/>
       <c r="CG23" t="inlineStr"/>
-      <c r="CH23" t="inlineStr"/>
-      <c r="CI23" t="inlineStr"/>
-      <c r="CJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4245,32 +4246,29 @@
       <c r="BR24" t="inlineStr"/>
       <c r="BS24" t="inlineStr"/>
       <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
-      <c r="BW24" t="n">
+      <c r="BU24" t="n">
         <v>728</v>
       </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>Saper eseguire con il proprio corpo i movimenti programmati, seguendo il ritmo della musica scelta.</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr"/>
       <c r="BX24" t="inlineStr">
         <is>
-          <t>Saper eseguire con il proprio corpo i movimenti programmati, seguendo il ritmo della musica scelta.</t>
+          <t>X</t>
         </is>
       </c>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="inlineStr"/>
-      <c r="CA24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CA24" t="inlineStr"/>
       <c r="CB24" t="inlineStr"/>
       <c r="CC24" t="inlineStr"/>
       <c r="CD24" t="inlineStr"/>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="inlineStr"/>
       <c r="CG24" t="inlineStr"/>
-      <c r="CH24" t="inlineStr"/>
-      <c r="CI24" t="inlineStr"/>
-      <c r="CJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4414,17 +4412,17 @@
       </c>
       <c r="BS25" t="inlineStr"/>
       <c r="BT25" t="inlineStr"/>
-      <c r="BU25" t="inlineStr"/>
-      <c r="BV25" t="inlineStr"/>
-      <c r="BW25" t="n">
+      <c r="BU25" t="n">
         <v>730</v>
       </c>
-      <c r="BX25" t="inlineStr">
+      <c r="BV25" t="inlineStr">
         <is>
           <t>funzionalità a problemi concreti (riproducibili non solo al computer) dei programmi informatici
 Dal mondo reale agli universi geometrici</t>
         </is>
       </c>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="inlineStr"/>
       <c r="CA25" t="inlineStr"/>
@@ -4434,9 +4432,6 @@
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="inlineStr"/>
       <c r="CG25" t="inlineStr"/>
-      <c r="CH25" t="inlineStr"/>
-      <c r="CI25" t="inlineStr"/>
-      <c r="CJ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4491,7 +4486,11 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
@@ -4521,11 +4520,7 @@
         </is>
       </c>
       <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
       <c r="BD26" t="inlineStr"/>
@@ -4561,17 +4556,17 @@
         </is>
       </c>
       <c r="BT26" t="inlineStr"/>
-      <c r="BU26" t="inlineStr"/>
-      <c r="BV26" t="inlineStr"/>
-      <c r="BW26" t="n">
+      <c r="BU26" t="n">
         <v>736</v>
       </c>
-      <c r="BX26" t="inlineStr">
+      <c r="BV26" t="inlineStr">
         <is>
           <t>Conoscenze acquisite in altre aree disciplinari
 Capacità di risolvere problemi</t>
         </is>
       </c>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="inlineStr"/>
       <c r="CA26" t="inlineStr"/>
@@ -4581,9 +4576,6 @@
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="inlineStr"/>
       <c r="CG26" t="inlineStr"/>
-      <c r="CH26" t="inlineStr"/>
-      <c r="CI26" t="inlineStr"/>
-      <c r="CJ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4698,16 +4690,16 @@
       <c r="BR27" t="inlineStr"/>
       <c r="BS27" t="inlineStr"/>
       <c r="BT27" t="inlineStr"/>
-      <c r="BU27" t="inlineStr"/>
-      <c r="BV27" t="inlineStr"/>
-      <c r="BW27" t="n">
+      <c r="BU27" t="n">
         <v>738</v>
       </c>
-      <c r="BX27" t="inlineStr">
+      <c r="BV27" t="inlineStr">
         <is>
           <t>Obiettivi indicati nelle attività sul programma il futuro e code . Org</t>
         </is>
       </c>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="inlineStr"/>
       <c r="CA27" t="inlineStr"/>
@@ -4715,15 +4707,12 @@
       <c r="CC27" t="inlineStr"/>
       <c r="CD27" t="inlineStr"/>
       <c r="CE27" t="inlineStr"/>
-      <c r="CF27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CG27" t="inlineStr"/>
-      <c r="CH27" t="inlineStr"/>
-      <c r="CI27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CJ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4834,27 +4823,24 @@
       <c r="BR28" t="inlineStr"/>
       <c r="BS28" t="inlineStr"/>
       <c r="BT28" t="inlineStr"/>
-      <c r="BU28" t="inlineStr"/>
-      <c r="BV28" t="inlineStr"/>
-      <c r="BW28" t="n">
+      <c r="BU28" t="n">
         <v>740</v>
       </c>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="inlineStr"/>
       <c r="CA28" t="inlineStr"/>
       <c r="CB28" t="inlineStr"/>
       <c r="CC28" t="inlineStr"/>
       <c r="CD28" t="inlineStr"/>
-      <c r="CE28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF28" t="inlineStr"/>
       <c r="CG28" t="inlineStr"/>
-      <c r="CH28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI28" t="inlineStr"/>
-      <c r="CJ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4921,17 +4907,21 @@
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
@@ -4962,7 +4952,11 @@
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr"/>
@@ -4985,28 +4979,20 @@
       <c r="BQ29" t="inlineStr"/>
       <c r="BR29" t="inlineStr"/>
       <c r="BS29" t="inlineStr"/>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr"/>
-      <c r="BV29" t="inlineStr"/>
-      <c r="BW29" t="n">
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="n">
         <v>744</v>
       </c>
-      <c r="BX29" t="inlineStr">
+      <c r="BV29" t="inlineStr">
         <is>
           <t>Allenare il pensiero divergente (spesso la soluzione più evidente non è quella corretta).
 Collaborare con i compagni.
 Imparare ad esprimersi correttamente</t>
         </is>
       </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="inlineStr"/>
       <c r="CA29" t="inlineStr"/>
       <c r="CB29" t="inlineStr"/>
@@ -5015,9 +5001,6 @@
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="inlineStr"/>
       <c r="CG29" t="inlineStr"/>
-      <c r="CH29" t="inlineStr"/>
-      <c r="CI29" t="inlineStr"/>
-      <c r="CJ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5196,27 +5179,24 @@
       <c r="BR30" t="inlineStr"/>
       <c r="BS30" t="inlineStr"/>
       <c r="BT30" t="inlineStr"/>
-      <c r="BU30" t="inlineStr"/>
-      <c r="BV30" t="inlineStr"/>
-      <c r="BW30" t="n">
+      <c r="BU30" t="n">
         <v>745</v>
       </c>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="inlineStr"/>
       <c r="CA30" t="inlineStr"/>
       <c r="CB30" t="inlineStr"/>
       <c r="CC30" t="inlineStr"/>
       <c r="CD30" t="inlineStr"/>
-      <c r="CE30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF30" t="inlineStr"/>
       <c r="CG30" t="inlineStr"/>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr"/>
-      <c r="CJ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5320,16 +5300,16 @@
       <c r="BR31" t="inlineStr"/>
       <c r="BS31" t="inlineStr"/>
       <c r="BT31" t="inlineStr"/>
-      <c r="BU31" t="inlineStr"/>
-      <c r="BV31" t="inlineStr"/>
-      <c r="BW31" t="n">
+      <c r="BU31" t="n">
         <v>747</v>
       </c>
-      <c r="BX31" t="inlineStr">
+      <c r="BV31" t="inlineStr">
         <is>
           <t>Tutti gli obiettivi possibili</t>
         </is>
       </c>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="inlineStr"/>
       <c r="CA31" t="inlineStr"/>
@@ -5337,15 +5317,12 @@
       <c r="CC31" t="inlineStr"/>
       <c r="CD31" t="inlineStr"/>
       <c r="CE31" t="inlineStr"/>
-      <c r="CF31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CG31" t="inlineStr"/>
-      <c r="CH31" t="inlineStr"/>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CJ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5469,32 +5446,29 @@
       <c r="BR32" t="inlineStr"/>
       <c r="BS32" t="inlineStr"/>
       <c r="BT32" t="inlineStr"/>
-      <c r="BU32" t="inlineStr"/>
-      <c r="BV32" t="inlineStr"/>
-      <c r="BW32" t="n">
+      <c r="BU32" t="n">
         <v>749</v>
       </c>
-      <c r="BX32" t="inlineStr">
+      <c r="BV32" t="inlineStr">
         <is>
           <t>Analizzare i dati e la loro organizzazione; rappresentare le informazioni attraverso codici; costruire sequenze di istruzioni per risolvere i problemi.</t>
         </is>
       </c>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="inlineStr"/>
       <c r="CA32" t="inlineStr"/>
       <c r="CB32" t="inlineStr"/>
       <c r="CC32" t="inlineStr"/>
-      <c r="CD32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CE32" t="inlineStr"/>
       <c r="CF32" t="inlineStr"/>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr"/>
-      <c r="CI32" t="inlineStr"/>
-      <c r="CJ32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5605,27 +5579,24 @@
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="inlineStr"/>
       <c r="BT33" t="inlineStr"/>
-      <c r="BU33" t="inlineStr"/>
-      <c r="BV33" t="inlineStr"/>
-      <c r="BW33" t="n">
+      <c r="BU33" t="n">
         <v>756</v>
       </c>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="inlineStr"/>
       <c r="CA33" t="inlineStr"/>
       <c r="CB33" t="inlineStr"/>
       <c r="CC33" t="inlineStr"/>
       <c r="CD33" t="inlineStr"/>
-      <c r="CE33" t="inlineStr"/>
+      <c r="CE33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF33" t="inlineStr"/>
       <c r="CG33" t="inlineStr"/>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr"/>
-      <c r="CJ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5779,11 +5750,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BA34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr">
         <is>
@@ -5827,12 +5794,10 @@
       <c r="BR34" t="inlineStr"/>
       <c r="BS34" t="inlineStr"/>
       <c r="BT34" t="inlineStr"/>
-      <c r="BU34" t="inlineStr"/>
-      <c r="BV34" t="inlineStr"/>
-      <c r="BW34" t="n">
+      <c r="BU34" t="n">
         <v>759</v>
       </c>
-      <c r="BX34" t="inlineStr">
+      <c r="BV34" t="inlineStr">
         <is>
           <t>Conoscere e utilizzare i blocchi di Scratch per creare movimenti, dialoghi e interazioni tra i personaggi.
 Essere in grado di aggiungere, modificare e personalizzare i personaggi e gli sfondi in Scratch.
@@ -5846,11 +5811,9 @@
 Riflettere sull'esperienza, discutendo cosa è stato appreso e cosa si potrebbe migliorare in futuro.</t>
         </is>
       </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="inlineStr"/>
       <c r="CA34" t="inlineStr"/>
       <c r="CB34" t="inlineStr"/>
@@ -5859,9 +5822,6 @@
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="inlineStr"/>
       <c r="CG34" t="inlineStr"/>
-      <c r="CH34" t="inlineStr"/>
-      <c r="CI34" t="inlineStr"/>
-      <c r="CJ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6009,34 +5969,31 @@
       <c r="BR35" t="inlineStr"/>
       <c r="BS35" t="inlineStr"/>
       <c r="BT35" t="inlineStr"/>
-      <c r="BU35" t="inlineStr"/>
-      <c r="BV35" t="inlineStr"/>
-      <c r="BW35" t="n">
+      <c r="BU35" t="n">
         <v>766</v>
       </c>
-      <c r="BX35" t="inlineStr">
+      <c r="BV35" t="inlineStr">
         <is>
           <t>Storia: stagioni, mesi, giorni della settimana.
 Geografia: indicatori topologici.
 Matematica: sequenzialità, percorsi.</t>
         </is>
       </c>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="inlineStr"/>
       <c r="CA35" t="inlineStr"/>
       <c r="CB35" t="inlineStr"/>
-      <c r="CC35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CD35" t="inlineStr"/>
       <c r="CE35" t="inlineStr"/>
-      <c r="CF35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CF35" t="inlineStr"/>
       <c r="CG35" t="inlineStr"/>
-      <c r="CH35" t="inlineStr"/>
-      <c r="CI35" t="inlineStr"/>
-      <c r="CJ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6084,11 +6041,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -6153,22 +6106,22 @@
       <c r="BQ36" t="inlineStr"/>
       <c r="BR36" t="inlineStr"/>
       <c r="BS36" t="inlineStr"/>
-      <c r="BT36" t="inlineStr"/>
-      <c r="BU36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BV36" t="inlineStr"/>
-      <c r="BW36" t="n">
+      <c r="BT36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BU36" t="n">
         <v>767</v>
       </c>
-      <c r="BX36" t="inlineStr">
+      <c r="BV36" t="inlineStr">
         <is>
           <t>sviluppare il pensiero logico
 migliorare la competenza relazionale</t>
         </is>
       </c>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="inlineStr"/>
       <c r="CA36" t="inlineStr"/>
@@ -6178,9 +6131,6 @@
       <c r="CE36" t="inlineStr"/>
       <c r="CF36" t="inlineStr"/>
       <c r="CG36" t="inlineStr"/>
-      <c r="CH36" t="inlineStr"/>
-      <c r="CI36" t="inlineStr"/>
-      <c r="CJ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6309,16 +6259,16 @@
       <c r="BR37" t="inlineStr"/>
       <c r="BS37" t="inlineStr"/>
       <c r="BT37" t="inlineStr"/>
-      <c r="BU37" t="inlineStr"/>
-      <c r="BV37" t="inlineStr"/>
-      <c r="BW37" t="n">
+      <c r="BU37" t="n">
         <v>773</v>
       </c>
-      <c r="BX37" t="inlineStr">
+      <c r="BV37" t="inlineStr">
         <is>
           <t>Avvio alla operazioni sulla retta dei numeri; consolidamento del concetto di sequanzialità nella numerazione e della cordialità</t>
         </is>
       </c>
+      <c r="BW37" t="inlineStr"/>
+      <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="inlineStr"/>
       <c r="CA37" t="inlineStr"/>
@@ -6328,9 +6278,6 @@
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="inlineStr"/>
       <c r="CG37" t="inlineStr"/>
-      <c r="CH37" t="inlineStr"/>
-      <c r="CI37" t="inlineStr"/>
-      <c r="CJ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6444,21 +6391,17 @@
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr"/>
       <c r="BT38" t="inlineStr"/>
-      <c r="BU38" t="inlineStr"/>
-      <c r="BV38" t="inlineStr"/>
-      <c r="BW38" t="n">
+      <c r="BU38" t="n">
         <v>774</v>
       </c>
-      <c r="BX38" t="inlineStr">
+      <c r="BV38" t="inlineStr">
         <is>
           <t>esprimersi e comunicare utilizzando un linguaggio specifico, riferire semplici istruzioni legate alla quotidianità. Indicare la destra e la sinistra rispetto al personaggio da muovere sullo schermo.</t>
         </is>
       </c>
-      <c r="BY38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="inlineStr"/>
       <c r="CA38" t="inlineStr"/>
       <c r="CB38" t="inlineStr"/>
@@ -6466,10 +6409,7 @@
       <c r="CD38" t="inlineStr"/>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="inlineStr"/>
-      <c r="CG38" t="inlineStr"/>
-      <c r="CH38" t="inlineStr"/>
-      <c r="CI38" t="inlineStr"/>
-      <c r="CJ38" t="inlineStr">
+      <c r="CG38" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -6553,7 +6493,11 @@
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE39" t="inlineStr">
         <is>
           <t>X</t>
@@ -6637,7 +6581,11 @@
       <c r="BN39" t="inlineStr"/>
       <c r="BO39" t="inlineStr"/>
       <c r="BP39" t="inlineStr"/>
-      <c r="BQ39" t="inlineStr"/>
+      <c r="BQ39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BR39" t="inlineStr"/>
       <c r="BS39" t="inlineStr"/>
       <c r="BT39" t="inlineStr">
@@ -6645,20 +6593,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BU39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="BU39" t="n">
+        <v>779</v>
       </c>
       <c r="BV39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BW39" t="n">
-        <v>779</v>
-      </c>
-      <c r="BX39" t="inlineStr">
         <is>
           <t>Riconoscere e risolvere problemi.
 Sviluppare capacità di osservazione, di memoria, di analisi.
@@ -6668,6 +6606,8 @@
 Migliorare la precisione e il rigore nello svolgimento dei compiti.</t>
         </is>
       </c>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="inlineStr"/>
       <c r="CA39" t="inlineStr"/>
@@ -6677,9 +6617,6 @@
       <c r="CE39" t="inlineStr"/>
       <c r="CF39" t="inlineStr"/>
       <c r="CG39" t="inlineStr"/>
-      <c r="CH39" t="inlineStr"/>
-      <c r="CI39" t="inlineStr"/>
-      <c r="CJ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6760,7 +6697,11 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
@@ -6801,11 +6742,7 @@
         </is>
       </c>
       <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA40" t="inlineStr"/>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr"/>
       <c r="BD40" t="inlineStr"/>
@@ -6837,16 +6774,16 @@
       <c r="BR40" t="inlineStr"/>
       <c r="BS40" t="inlineStr"/>
       <c r="BT40" t="inlineStr"/>
-      <c r="BU40" t="inlineStr"/>
-      <c r="BV40" t="inlineStr"/>
-      <c r="BW40" t="n">
+      <c r="BU40" t="n">
         <v>784</v>
       </c>
-      <c r="BX40" t="inlineStr">
+      <c r="BV40" t="inlineStr">
         <is>
           <t>Orientarsi nello spazio consolidando i concetti di destra e sinistra, problem solving, cooperative learning, correzione dell'errore.</t>
         </is>
       </c>
+      <c r="BW40" t="inlineStr"/>
+      <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="inlineStr"/>
       <c r="CA40" t="inlineStr"/>
@@ -6856,9 +6793,6 @@
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="inlineStr"/>
       <c r="CG40" t="inlineStr"/>
-      <c r="CH40" t="inlineStr"/>
-      <c r="CI40" t="inlineStr"/>
-      <c r="CJ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6957,16 +6891,16 @@
       <c r="BR41" t="inlineStr"/>
       <c r="BS41" t="inlineStr"/>
       <c r="BT41" t="inlineStr"/>
-      <c r="BU41" t="inlineStr"/>
-      <c r="BV41" t="inlineStr"/>
-      <c r="BW41" t="n">
+      <c r="BU41" t="n">
         <v>788</v>
       </c>
-      <c r="BX41" t="inlineStr">
+      <c r="BV41" t="inlineStr">
         <is>
           <t>Competenze digitali</t>
         </is>
       </c>
+      <c r="BW41" t="inlineStr"/>
+      <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="inlineStr"/>
       <c r="CA41" t="inlineStr"/>
@@ -6974,15 +6908,12 @@
       <c r="CC41" t="inlineStr"/>
       <c r="CD41" t="inlineStr"/>
       <c r="CE41" t="inlineStr"/>
-      <c r="CF41" t="inlineStr"/>
+      <c r="CF41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CG41" t="inlineStr"/>
-      <c r="CH41" t="inlineStr"/>
-      <c r="CI41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CJ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7097,16 +7028,16 @@
       <c r="BR42" t="inlineStr"/>
       <c r="BS42" t="inlineStr"/>
       <c r="BT42" t="inlineStr"/>
-      <c r="BU42" t="inlineStr"/>
-      <c r="BV42" t="inlineStr"/>
-      <c r="BW42" t="n">
+      <c r="BU42" t="n">
         <v>791</v>
       </c>
-      <c r="BX42" t="inlineStr">
+      <c r="BV42" t="inlineStr">
         <is>
           <t>Sulla possibilità di usare il linguaggio informatico fatto di simboli e altro per elaborare altre attività.</t>
         </is>
       </c>
+      <c r="BW42" t="inlineStr"/>
+      <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="inlineStr"/>
       <c r="CA42" t="inlineStr"/>
@@ -7116,9 +7047,6 @@
       <c r="CE42" t="inlineStr"/>
       <c r="CF42" t="inlineStr"/>
       <c r="CG42" t="inlineStr"/>
-      <c r="CH42" t="inlineStr"/>
-      <c r="CI42" t="inlineStr"/>
-      <c r="CJ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -7226,32 +7154,29 @@
       <c r="BR43" t="inlineStr"/>
       <c r="BS43" t="inlineStr"/>
       <c r="BT43" t="inlineStr"/>
-      <c r="BU43" t="inlineStr"/>
-      <c r="BV43" t="inlineStr"/>
-      <c r="BW43" t="n">
+      <c r="BU43" t="n">
         <v>548</v>
       </c>
-      <c r="BX43" t="inlineStr">
+      <c r="BV43" t="inlineStr">
         <is>
           <t>Salvaguardia  della Terra: flora, fauna, biodiversità, ecosistemi ...</t>
         </is>
       </c>
-      <c r="BY43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BZ43" t="inlineStr"/>
       <c r="CA43" t="inlineStr"/>
-      <c r="CB43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="CB43" t="inlineStr"/>
       <c r="CC43" t="inlineStr"/>
       <c r="CD43" t="inlineStr"/>
       <c r="CE43" t="inlineStr"/>
       <c r="CF43" t="inlineStr"/>
       <c r="CG43" t="inlineStr"/>
-      <c r="CH43" t="inlineStr"/>
-      <c r="CI43" t="inlineStr"/>
-      <c r="CJ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7367,27 +7292,24 @@
       </c>
       <c r="BS44" t="inlineStr"/>
       <c r="BT44" t="inlineStr"/>
-      <c r="BU44" t="inlineStr"/>
-      <c r="BV44" t="inlineStr"/>
-      <c r="BW44" t="n">
+      <c r="BU44" t="n">
         <v>550</v>
       </c>
+      <c r="BW44" t="inlineStr"/>
+      <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="inlineStr"/>
       <c r="CA44" t="inlineStr"/>
       <c r="CB44" t="inlineStr"/>
       <c r="CC44" t="inlineStr"/>
       <c r="CD44" t="inlineStr"/>
-      <c r="CE44" t="inlineStr"/>
+      <c r="CE44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF44" t="inlineStr"/>
       <c r="CG44" t="inlineStr"/>
-      <c r="CH44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI44" t="inlineStr"/>
-      <c r="CJ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7454,14 +7376,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
@@ -7509,14 +7431,14 @@
         </is>
       </c>
       <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE45" t="inlineStr"/>
       <c r="BF45" t="inlineStr"/>
       <c r="BG45" t="inlineStr"/>
@@ -7545,27 +7467,23 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BU45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BV45" t="inlineStr"/>
-      <c r="BW45" t="n">
+      <c r="BU45" t="n">
         <v>553</v>
       </c>
-      <c r="BX45" t="inlineStr">
+      <c r="BV45" t="inlineStr">
         <is>
           <t>tentativi per errore
 competenze linguistiche, logico- matematiche, spazialità, Problem solving</t>
         </is>
       </c>
+      <c r="BW45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
-      <c r="BZ45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BZ45" t="inlineStr"/>
       <c r="CA45" t="inlineStr"/>
       <c r="CB45" t="inlineStr"/>
       <c r="CC45" t="inlineStr"/>
@@ -7573,9 +7491,6 @@
       <c r="CE45" t="inlineStr"/>
       <c r="CF45" t="inlineStr"/>
       <c r="CG45" t="inlineStr"/>
-      <c r="CH45" t="inlineStr"/>
-      <c r="CI45" t="inlineStr"/>
-      <c r="CJ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7632,11 +7547,19 @@
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
@@ -7661,11 +7584,7 @@
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr"/>
       <c r="BD46" t="inlineStr"/>
@@ -7692,22 +7611,18 @@
       <c r="BQ46" t="inlineStr"/>
       <c r="BR46" t="inlineStr"/>
       <c r="BS46" t="inlineStr"/>
-      <c r="BT46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU46" t="inlineStr"/>
-      <c r="BV46" t="inlineStr"/>
-      <c r="BW46" t="n">
+      <c r="BT46" t="inlineStr"/>
+      <c r="BU46" t="n">
         <v>556</v>
       </c>
-      <c r="BX46" t="inlineStr">
+      <c r="BV46" t="inlineStr">
         <is>
           <t>Promuovere differenti strategie di risoluzione di problemi;
 Collaborare e cooperare per giungere alla soluzione.</t>
         </is>
       </c>
+      <c r="BW46" t="inlineStr"/>
+      <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="inlineStr"/>
       <c r="CA46" t="inlineStr"/>
@@ -7717,9 +7632,6 @@
       <c r="CE46" t="inlineStr"/>
       <c r="CF46" t="inlineStr"/>
       <c r="CG46" t="inlineStr"/>
-      <c r="CH46" t="inlineStr"/>
-      <c r="CI46" t="inlineStr"/>
-      <c r="CJ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7819,27 +7731,24 @@
       <c r="BR47" t="inlineStr"/>
       <c r="BS47" t="inlineStr"/>
       <c r="BT47" t="inlineStr"/>
-      <c r="BU47" t="inlineStr"/>
-      <c r="BV47" t="inlineStr"/>
-      <c r="BW47" t="n">
+      <c r="BU47" t="n">
         <v>569</v>
       </c>
+      <c r="BW47" t="inlineStr"/>
+      <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="inlineStr"/>
       <c r="CA47" t="inlineStr"/>
       <c r="CB47" t="inlineStr"/>
       <c r="CC47" t="inlineStr"/>
       <c r="CD47" t="inlineStr"/>
-      <c r="CE47" t="inlineStr"/>
+      <c r="CE47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF47" t="inlineStr"/>
       <c r="CG47" t="inlineStr"/>
-      <c r="CH47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI47" t="inlineStr"/>
-      <c r="CJ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7942,21 +7851,17 @@
       <c r="BR48" t="inlineStr"/>
       <c r="BS48" t="inlineStr"/>
       <c r="BT48" t="inlineStr"/>
-      <c r="BU48" t="inlineStr"/>
-      <c r="BV48" t="inlineStr"/>
-      <c r="BW48" t="n">
+      <c r="BU48" t="n">
         <v>570</v>
       </c>
-      <c r="BX48" t="inlineStr">
+      <c r="BV48" t="inlineStr">
         <is>
           <t>Utilizzo la metodologia come parte integrante di tutte le mie lezioni, per cui associarla solo ad alcuni obiettivi di apprendimento sarebbe limitante. Gli studenti fin dalla prima usano diversi webtools e app2.0 anche per creare essi stessi lezioni, gamification e presentazioni.</t>
         </is>
       </c>
-      <c r="BY48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="inlineStr"/>
       <c r="CA48" t="inlineStr"/>
       <c r="CB48" t="inlineStr"/>
@@ -7965,9 +7870,6 @@
       <c r="CE48" t="inlineStr"/>
       <c r="CF48" t="inlineStr"/>
       <c r="CG48" t="inlineStr"/>
-      <c r="CH48" t="inlineStr"/>
-      <c r="CI48" t="inlineStr"/>
-      <c r="CJ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8069,16 +7971,16 @@
       <c r="BR49" t="inlineStr"/>
       <c r="BS49" t="inlineStr"/>
       <c r="BT49" t="inlineStr"/>
-      <c r="BU49" t="inlineStr"/>
-      <c r="BV49" t="inlineStr"/>
-      <c r="BW49" t="n">
+      <c r="BU49" t="n">
         <v>572</v>
       </c>
-      <c r="BX49" t="inlineStr">
+      <c r="BV49" t="inlineStr">
         <is>
           <t>Dx e sx, punti cardinale, percorsi</t>
         </is>
       </c>
+      <c r="BW49" t="inlineStr"/>
+      <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="inlineStr"/>
       <c r="CA49" t="inlineStr"/>
@@ -8088,9 +7990,6 @@
       <c r="CE49" t="inlineStr"/>
       <c r="CF49" t="inlineStr"/>
       <c r="CG49" t="inlineStr"/>
-      <c r="CH49" t="inlineStr"/>
-      <c r="CI49" t="inlineStr"/>
-      <c r="CJ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8139,18 +8038,18 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="AH50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
@@ -8181,18 +8080,18 @@
         </is>
       </c>
       <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA50" t="inlineStr"/>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE50" t="inlineStr"/>
       <c r="BF50" t="inlineStr"/>
       <c r="BG50" t="inlineStr"/>
@@ -8213,17 +8112,17 @@
       <c r="BR50" t="inlineStr"/>
       <c r="BS50" t="inlineStr"/>
       <c r="BT50" t="inlineStr"/>
-      <c r="BU50" t="inlineStr"/>
-      <c r="BV50" t="inlineStr"/>
-      <c r="BW50" t="n">
+      <c r="BU50" t="n">
         <v>580</v>
       </c>
-      <c r="BX50" t="inlineStr">
+      <c r="BV50" t="inlineStr">
         <is>
           <t>Logica
 Problem solving</t>
         </is>
       </c>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="inlineStr"/>
       <c r="CA50" t="inlineStr"/>
@@ -8233,9 +8132,6 @@
       <c r="CE50" t="inlineStr"/>
       <c r="CF50" t="inlineStr"/>
       <c r="CG50" t="inlineStr"/>
-      <c r="CH50" t="inlineStr"/>
-      <c r="CI50" t="inlineStr"/>
-      <c r="CJ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8288,12 +8184,12 @@
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8329,7 +8225,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE51" t="inlineStr"/>
       <c r="BF51" t="inlineStr">
         <is>
@@ -8357,17 +8257,11 @@
       <c r="BQ51" t="inlineStr"/>
       <c r="BR51" t="inlineStr"/>
       <c r="BS51" t="inlineStr"/>
-      <c r="BT51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU51" t="inlineStr"/>
-      <c r="BV51" t="inlineStr"/>
-      <c r="BW51" t="n">
+      <c r="BT51" t="inlineStr"/>
+      <c r="BU51" t="n">
         <v>581</v>
       </c>
-      <c r="BX51" t="inlineStr">
+      <c r="BV51" t="inlineStr">
         <is>
           <t>Costruzione di un testo
 Comprensione del testo 
@@ -8376,12 +8270,14 @@
 Collaborare per la realizzazione di un progetto comune</t>
         </is>
       </c>
+      <c r="BW51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
-      <c r="BZ51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BZ51" t="inlineStr"/>
       <c r="CA51" t="inlineStr"/>
       <c r="CB51" t="inlineStr"/>
       <c r="CC51" t="inlineStr"/>
@@ -8389,9 +8285,6 @@
       <c r="CE51" t="inlineStr"/>
       <c r="CF51" t="inlineStr"/>
       <c r="CG51" t="inlineStr"/>
-      <c r="CH51" t="inlineStr"/>
-      <c r="CI51" t="inlineStr"/>
-      <c r="CJ51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8509,20 +8402,16 @@
       </c>
       <c r="BS52" t="inlineStr"/>
       <c r="BT52" t="inlineStr"/>
-      <c r="BU52" t="inlineStr"/>
+      <c r="BU52" t="n">
+        <v>582</v>
+      </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BW52" t="n">
-        <v>582</v>
-      </c>
-      <c r="BX52" t="inlineStr">
-        <is>
           <t>Avvio alla conoscenza dello strumento o dell'app, funzione e utilità, applicazione pratica e capacità di discernere e trovare l'applicazione durante l'azione didattica</t>
         </is>
       </c>
+      <c r="BW52" t="inlineStr"/>
+      <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="inlineStr"/>
       <c r="CA52" t="inlineStr"/>
@@ -8532,9 +8421,6 @@
       <c r="CE52" t="inlineStr"/>
       <c r="CF52" t="inlineStr"/>
       <c r="CG52" t="inlineStr"/>
-      <c r="CH52" t="inlineStr"/>
-      <c r="CI52" t="inlineStr"/>
-      <c r="CJ52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8592,7 +8478,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
@@ -8621,11 +8511,7 @@
         </is>
       </c>
       <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA53" t="inlineStr"/>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr"/>
       <c r="BD53" t="inlineStr"/>
@@ -8649,16 +8535,16 @@
       <c r="BR53" t="inlineStr"/>
       <c r="BS53" t="inlineStr"/>
       <c r="BT53" t="inlineStr"/>
-      <c r="BU53" t="inlineStr"/>
-      <c r="BV53" t="inlineStr"/>
-      <c r="BW53" t="n">
+      <c r="BU53" t="n">
         <v>584</v>
       </c>
-      <c r="BX53" t="inlineStr">
+      <c r="BV53" t="inlineStr">
         <is>
           <t>Migliorare le abilità informatiche</t>
         </is>
       </c>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="inlineStr"/>
       <c r="CA53" t="inlineStr"/>
@@ -8666,15 +8552,12 @@
       <c r="CC53" t="inlineStr"/>
       <c r="CD53" t="inlineStr"/>
       <c r="CE53" t="inlineStr"/>
-      <c r="CF53" t="inlineStr"/>
+      <c r="CF53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CG53" t="inlineStr"/>
-      <c r="CH53" t="inlineStr"/>
-      <c r="CI53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CJ53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8743,7 +8626,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
@@ -8781,11 +8668,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="BA54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr"/>
       <c r="BD54" t="inlineStr"/>
@@ -8813,22 +8696,22 @@
       <c r="BR54" t="inlineStr"/>
       <c r="BS54" t="inlineStr"/>
       <c r="BT54" t="inlineStr"/>
-      <c r="BU54" t="inlineStr"/>
-      <c r="BV54" t="inlineStr"/>
-      <c r="BW54" t="n">
+      <c r="BU54" t="n">
         <v>589</v>
       </c>
-      <c r="BX54" t="inlineStr">
+      <c r="BV54" t="inlineStr">
         <is>
           <t>Aumentare il grado di astrazione riguardo ai concetti di avanti, indietro, gira a destra, gira a sinistra.</t>
         </is>
       </c>
+      <c r="BW54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
-      <c r="BZ54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BZ54" t="inlineStr"/>
       <c r="CA54" t="inlineStr"/>
       <c r="CB54" t="inlineStr"/>
       <c r="CC54" t="inlineStr"/>
@@ -8836,9 +8719,6 @@
       <c r="CE54" t="inlineStr"/>
       <c r="CF54" t="inlineStr"/>
       <c r="CG54" t="inlineStr"/>
-      <c r="CH54" t="inlineStr"/>
-      <c r="CI54" t="inlineStr"/>
-      <c r="CJ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8893,7 +8773,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
@@ -8918,11 +8802,7 @@
         </is>
       </c>
       <c r="AZ55" t="inlineStr"/>
-      <c r="BA55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr"/>
       <c r="BD55" t="inlineStr"/>
@@ -8946,27 +8826,24 @@
       <c r="BR55" t="inlineStr"/>
       <c r="BS55" t="inlineStr"/>
       <c r="BT55" t="inlineStr"/>
-      <c r="BU55" t="inlineStr"/>
-      <c r="BV55" t="inlineStr"/>
-      <c r="BW55" t="n">
+      <c r="BU55" t="n">
         <v>603</v>
       </c>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="inlineStr"/>
       <c r="CA55" t="inlineStr"/>
       <c r="CB55" t="inlineStr"/>
       <c r="CC55" t="inlineStr"/>
       <c r="CD55" t="inlineStr"/>
-      <c r="CE55" t="inlineStr"/>
+      <c r="CE55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF55" t="inlineStr"/>
       <c r="CG55" t="inlineStr"/>
-      <c r="CH55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI55" t="inlineStr"/>
-      <c r="CJ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -9008,11 +8885,19 @@
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
@@ -9041,11 +8926,7 @@
         </is>
       </c>
       <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA56" t="inlineStr"/>
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr"/>
       <c r="BD56" t="inlineStr">
@@ -9072,21 +8953,17 @@
       <c r="BQ56" t="inlineStr"/>
       <c r="BR56" t="inlineStr"/>
       <c r="BS56" t="inlineStr"/>
-      <c r="BT56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BU56" t="inlineStr"/>
-      <c r="BV56" t="inlineStr"/>
-      <c r="BW56" t="n">
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="n">
         <v>605</v>
       </c>
-      <c r="BX56" t="inlineStr">
+      <c r="BV56" t="inlineStr">
         <is>
           <t>lavorare in gruppo</t>
         </is>
       </c>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="inlineStr"/>
       <c r="CA56" t="inlineStr"/>
@@ -9096,9 +8973,6 @@
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="inlineStr"/>
       <c r="CG56" t="inlineStr"/>
-      <c r="CH56" t="inlineStr"/>
-      <c r="CI56" t="inlineStr"/>
-      <c r="CJ56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9238,18 +9112,18 @@
       <c r="BR57" t="inlineStr"/>
       <c r="BS57" t="inlineStr"/>
       <c r="BT57" t="inlineStr"/>
-      <c r="BU57" t="inlineStr"/>
-      <c r="BV57" t="inlineStr"/>
-      <c r="BW57" t="n">
+      <c r="BU57" t="n">
         <v>607</v>
       </c>
-      <c r="BX57" t="inlineStr">
+      <c r="BV57" t="inlineStr">
         <is>
           <t>-Utilizzare le espressioni condizionali se/allora
 -Aprire un programma, utilizzarlo, salvare il lavoro, riaprirlo
 -Costruire storie interattive, animazioni.</t>
         </is>
       </c>
+      <c r="BW57" t="inlineStr"/>
+      <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="inlineStr"/>
       <c r="CA57" t="inlineStr"/>
@@ -9259,9 +9133,6 @@
       <c r="CE57" t="inlineStr"/>
       <c r="CF57" t="inlineStr"/>
       <c r="CG57" t="inlineStr"/>
-      <c r="CH57" t="inlineStr"/>
-      <c r="CI57" t="inlineStr"/>
-      <c r="CJ57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9328,14 +9199,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
@@ -9361,14 +9232,14 @@
         </is>
       </c>
       <c r="AZ58" t="inlineStr"/>
-      <c r="BA58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA58" t="inlineStr"/>
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr"/>
-      <c r="BD58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE58" t="inlineStr"/>
       <c r="BF58" t="inlineStr">
         <is>
@@ -9392,17 +9263,15 @@
         </is>
       </c>
       <c r="BS58" t="inlineStr"/>
-      <c r="BT58" t="inlineStr"/>
-      <c r="BU58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="BV58" t="inlineStr"/>
-      <c r="BW58" t="n">
+      <c r="BT58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="BU58" t="n">
         <v>612</v>
       </c>
-      <c r="BX58" t="inlineStr">
+      <c r="BV58" t="inlineStr">
         <is>
           <t>-Comprensione del problema iniziale da risolvere
 - analisi delle fasi di risoluzione
@@ -9413,6 +9282,8 @@
 - Empatia</t>
         </is>
       </c>
+      <c r="BW58" t="inlineStr"/>
+      <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="inlineStr"/>
       <c r="CA58" t="inlineStr"/>
@@ -9422,9 +9293,6 @@
       <c r="CE58" t="inlineStr"/>
       <c r="CF58" t="inlineStr"/>
       <c r="CG58" t="inlineStr"/>
-      <c r="CH58" t="inlineStr"/>
-      <c r="CI58" t="inlineStr"/>
-      <c r="CJ58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9470,7 +9338,11 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
@@ -9499,11 +9371,7 @@
         </is>
       </c>
       <c r="AZ59" t="inlineStr"/>
-      <c r="BA59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA59" t="inlineStr"/>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr"/>
       <c r="BD59" t="inlineStr"/>
@@ -9523,27 +9391,24 @@
       <c r="BR59" t="inlineStr"/>
       <c r="BS59" t="inlineStr"/>
       <c r="BT59" t="inlineStr"/>
-      <c r="BU59" t="inlineStr"/>
-      <c r="BV59" t="inlineStr"/>
-      <c r="BW59" t="n">
+      <c r="BU59" t="n">
         <v>613</v>
       </c>
+      <c r="BW59" t="inlineStr"/>
+      <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="inlineStr"/>
       <c r="CA59" t="inlineStr"/>
       <c r="CB59" t="inlineStr"/>
       <c r="CC59" t="inlineStr"/>
       <c r="CD59" t="inlineStr"/>
-      <c r="CE59" t="inlineStr"/>
+      <c r="CE59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF59" t="inlineStr"/>
       <c r="CG59" t="inlineStr"/>
-      <c r="CH59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI59" t="inlineStr"/>
-      <c r="CJ59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9594,7 +9459,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AH60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
@@ -9623,11 +9492,7 @@
         </is>
       </c>
       <c r="AZ60" t="inlineStr"/>
-      <c r="BA60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="BA60" t="inlineStr"/>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr"/>
       <c r="BD60" t="inlineStr"/>
@@ -9651,27 +9516,24 @@
       <c r="BR60" t="inlineStr"/>
       <c r="BS60" t="inlineStr"/>
       <c r="BT60" t="inlineStr"/>
-      <c r="BU60" t="inlineStr"/>
-      <c r="BV60" t="inlineStr"/>
-      <c r="BW60" t="n">
+      <c r="BU60" t="n">
         <v>617</v>
       </c>
+      <c r="BW60" t="inlineStr"/>
+      <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="inlineStr"/>
       <c r="CA60" t="inlineStr"/>
       <c r="CB60" t="inlineStr"/>
       <c r="CC60" t="inlineStr"/>
       <c r="CD60" t="inlineStr"/>
-      <c r="CE60" t="inlineStr"/>
+      <c r="CE60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="CF60" t="inlineStr"/>
       <c r="CG60" t="inlineStr"/>
-      <c r="CH60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="CI60" t="inlineStr"/>
-      <c r="CJ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9811,16 +9673,16 @@
       <c r="BR61" t="inlineStr"/>
       <c r="BS61" t="inlineStr"/>
       <c r="BT61" t="inlineStr"/>
-      <c r="BU61" t="inlineStr"/>
-      <c r="BV61" t="inlineStr"/>
-      <c r="BW61" t="n">
+      <c r="BU61" t="n">
         <v>626</v>
       </c>
-      <c r="BX61" t="inlineStr">
+      <c r="BV61" t="inlineStr">
         <is>
           <t>Acquisizione concetti topologici e del punto di vista dell'altro.</t>
         </is>
       </c>
+      <c r="BW61" t="inlineStr"/>
+      <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="inlineStr"/>
       <c r="CA61" t="inlineStr"/>
@@ -9830,9 +9692,6 @@
       <c r="CE61" t="inlineStr"/>
       <c r="CF61" t="inlineStr"/>
       <c r="CG61" t="inlineStr"/>
-      <c r="CH61" t="inlineStr"/>
-      <c r="CI61" t="inlineStr"/>
-      <c r="CJ61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9876,11 +9735,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr">
         <is>
@@ -9923,7 +9778,11 @@
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
-      <c r="BD62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="BE62" t="inlineStr"/>
       <c r="BF62" t="inlineStr"/>
       <c r="BG62" t="inlineStr"/>
@@ -9940,17 +9799,17 @@
       <c r="BR62" t="inlineStr"/>
       <c r="BS62" t="inlineStr"/>
       <c r="BT62" t="inlineStr"/>
-      <c r="BU62" t="inlineStr"/>
-      <c r="BV62" t="inlineStr"/>
-      <c r="BW62" t="n">
+      <c r="BU62" t="n">
         <v>629</v>
       </c>
-      <c r="BX62" t="inlineStr">
+      <c r="BV62" t="inlineStr">
         <is>
           <t>SVILUPPARE LA LOGICA ATTRAVERSO IL GIOCO
 SVILUPPARE LA PERCEZIONE SPAZIALE</t>
         </is>
       </c>
+      <c r="BW62" t="inlineStr"/>
+      <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="inlineStr"/>
       <c r="CA62" t="inlineStr"/>
@@ -9960,9 +9819,6 @@
       <c r="CE62" t="inlineStr"/>
       <c r="CF62" t="inlineStr"/>
       <c r="CG62" t="inlineStr"/>
-      <c r="CH62" t="inlineStr"/>
-      <c r="CI62" t="inlineStr"/>
-      <c r="CJ62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
